--- a/tracking_forms/017_tire_contact_patch_measurement_form--tracking_forms.xlsx
+++ b/tracking_forms/017_tire_contact_patch_measurement_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_16}</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 16}</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_17}</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 17}</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_18}</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 18}</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'shop1'}</t>
+          <t>shop1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'shop1'}</t>
+          <t>shop1</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'shop2'}</t>
+          <t>shop2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'shop2'}</t>
+          <t>shop2</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'shop3'}</t>
+          <t>shop3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'shop3'}</t>
+          <t>shop3</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'other_technician'}</t>
+          <t>other_technician</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'other_technician'}</t>
+          <t>other technician</t>
         </is>
       </c>
     </row>
